--- a/data/trans_orig/P79$hipoteca_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P79$hipoteca_2023-Clase-trans_orig.xlsx
@@ -725,22 +725,22 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>5187</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1963</t>
+          <t>2130</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11581</t>
+          <t>13399</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,22 +760,22 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>4063</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1360</t>
+          <t>1505</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7898</t>
+          <t>9078</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>8881</t>
+          <t>9826</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4963</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16174</t>
+          <t>17258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>4890</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17405</t>
+          <t>22461</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,27 +873,27 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>3131</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>887</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7079</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>10296</t>
+          <t>13998</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5192</t>
+          <t>7507</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20068</t>
+          <t>24402</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>4903</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>4249</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2794</t>
+          <t>3037</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>721</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>8254</t>
+          <t>7772</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3381</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>874</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>8564</t>
+          <t>9711</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6418</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2533</t>
+          <t>2537</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>12036</t>
+          <t>12906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,26%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>14045</t>
+          <t>16201</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8553</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23370</t>
+          <t>25144</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,32 +1325,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15303</t>
+          <t>18273</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9506</t>
+          <t>11751</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23366</t>
+          <t>26964</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>29349</t>
+          <t>34474</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>25421</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>40886</t>
+          <t>46621</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1126</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1413,12 +1413,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6303</t>
+          <t>6026</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,32 +1438,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1864</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>507</t>
+          <t>641</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,27 +1473,27 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>3230</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>679</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>7425</t>
+          <t>8120</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11853</t>
+          <t>15237</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5917</t>
+          <t>8061</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20692</t>
+          <t>26007</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1777,32 +1777,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5309</t>
+          <t>6943</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2328</t>
+          <t>2957</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10918</t>
+          <t>13270</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1812,32 +1812,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>17162</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9925</t>
+          <t>14076</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29372</t>
+          <t>35161</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -1855,32 +1855,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>466612</t>
+          <t>503918</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>453694</t>
+          <t>487714</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>477724</t>
+          <t>514815</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1890,32 +1890,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>413214</t>
+          <t>447672</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>402929</t>
+          <t>437372</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>421265</t>
+          <t>457112</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1925,32 +1925,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>879827</t>
+          <t>951590</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>863022</t>
+          <t>932814</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>893450</t>
+          <t>965333</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>94,19%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>9172</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3956</t>
+          <t>4126</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>15738</t>
+          <t>18334</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4105</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1486</t>
+          <t>1594</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>9802</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>12403</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7159</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>20947</t>
+          <t>22046</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6921</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3006</t>
+          <t>2346</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12863</t>
+          <t>14773</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,17 +2155,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5242</t>
+          <t>5461</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18182</t>
+          <t>19409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -2198,7 +2198,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>936</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -2208,12 +2208,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>5002</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>936</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>4847</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2293,7 +2293,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,56%</t>
         </is>
       </c>
     </row>
@@ -2346,32 +2346,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1995</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11834</t>
+          <t>12171</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2381,32 +2381,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5042</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12031</t>
+          <t>12348</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1772</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2434,12 +2434,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>6238</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2449,7 +2449,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2006</t>
+          <t>2116</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>656</t>
+          <t>691</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2494,22 +2494,22 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3778</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1337</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8729</t>
+          <t>9509</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2537,32 +2537,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>25914</t>
+          <t>28103</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>19138</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37628</t>
+          <t>40430</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,44%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2572,32 +2572,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>28497</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17351</t>
+          <t>20274</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>34931</t>
+          <t>39585</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2607,32 +2607,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>51449</t>
+          <t>56600</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>40203</t>
+          <t>42516</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>65239</t>
+          <t>71201</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -2650,7 +2650,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2660,12 +2660,12 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7261</t>
+          <t>8950</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2675,7 +2675,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1577</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>612</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2833,7 +2833,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>549</t>
+          <t>612</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>2765</t>
+          <t>3036</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2989,32 +2989,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>9396</t>
+          <t>10123</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4497</t>
+          <t>4911</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16728</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3024,32 +3024,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11294</t>
+          <t>13713</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6517</t>
+          <t>8424</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17936</t>
+          <t>21268</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3059,32 +3059,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>20690</t>
+          <t>23836</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13509</t>
+          <t>15711</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>29799</t>
+          <t>34332</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -3102,32 +3102,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>403836</t>
+          <t>430714</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>390981</t>
+          <t>415899</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>414062</t>
+          <t>442623</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3137,32 +3137,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>332729</t>
+          <t>366917</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>320481</t>
+          <t>353253</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>343312</t>
+          <t>378118</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3172,32 +3172,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>736566</t>
+          <t>797632</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>719821</t>
+          <t>779869</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>751449</t>
+          <t>815281</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>91,13%</t>
+          <t>91,09%</t>
         </is>
       </c>
     </row>
@@ -3219,32 +3219,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>1994</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>11854</t>
+          <t>11892</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3289,32 +3289,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>5047</t>
+          <t>5494</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12827</t>
+          <t>12907</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -3332,32 +3332,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4629</t>
+          <t>7239</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>11283</t>
+          <t>14623</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3367,32 +3367,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1408</t>
+          <t>2668</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>737</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3585</t>
+          <t>6516</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3402,32 +3402,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>6037</t>
+          <t>9907</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1637</t>
+          <t>5016</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>12970</t>
+          <t>16588</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -3445,32 +3445,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>4974</t>
+          <t>6890</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>2627</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>11781</t>
+          <t>15015</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1334</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3747</t>
+          <t>4706</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3515,32 +3515,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>8224</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>3725</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>13215</t>
+          <t>18105</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -3558,32 +3558,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>495</t>
+          <t>2490</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13510</t>
+          <t>14978</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3628,32 +3628,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>6744</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>615</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>12438</t>
+          <t>15089</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -3671,32 +3671,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>8857</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1254</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18184</t>
+          <t>16482</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3706,32 +3706,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>2326</t>
+          <t>2571</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>555</t>
+          <t>620</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5295</t>
+          <t>6470</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3741,32 +3741,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>10916</t>
+          <t>11428</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>4023</t>
+          <t>6249</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>20500</t>
+          <t>20557</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>3,18%</t>
         </is>
       </c>
     </row>
@@ -3784,32 +3784,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>40275</t>
+          <t>45629</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>14197</t>
+          <t>34380</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>69254</t>
+          <t>59522</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3819,32 +3819,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>8491</t>
+          <t>8597</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>19623</t>
+          <t>21351</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3854,32 +3854,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>53132</t>
+          <t>60047</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>24697</t>
+          <t>46727</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>80798</t>
+          <t>75035</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>11,62%</t>
         </is>
       </c>
     </row>
@@ -3897,32 +3897,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>5831</t>
+          <t>6601</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>867</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>12583</t>
+          <t>13358</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3932,32 +3932,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2200</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>662</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5167</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3967,32 +3967,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>8801</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>4491</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>16074</t>
+          <t>16044</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,48%</t>
         </is>
       </c>
     </row>
@@ -4236,32 +4236,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>21914</t>
+          <t>24183</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>7334</t>
+          <t>16222</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>38324</t>
+          <t>35452</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4271,32 +4271,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>3128</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>1256</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>6483</t>
+          <t>9676</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4306,32 +4306,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>25042</t>
+          <t>28650</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>9413</t>
+          <t>20199</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>39705</t>
+          <t>39712</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>6,15%</t>
         </is>
       </c>
     </row>
@@ -4349,32 +4349,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>588768</t>
+          <t>380518</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>541543</t>
+          <t>364080</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>631179</t>
+          <t>395340</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4384,32 +4384,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>146702</t>
+          <t>163425</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>138659</t>
+          <t>154252</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>151935</t>
+          <t>170123</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>83,21%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>92,12%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4419,32 +4419,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>735469</t>
+          <t>543944</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>692622</t>
+          <t>524012</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>784540</t>
+          <t>560579</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>84,24%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>86,82%</t>
         </is>
       </c>
     </row>
@@ -4466,67 +4466,67 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>9603</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>4545</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>17047</t>
+          <t>19308</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
+          <t>0,47%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>7635</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>3715</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>13117</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>0,92%</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
           <t>0,45%</t>
         </is>
       </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>1,68%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>6564</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
-        <is>
-          <t>2453</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>12632</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4536,32 +4536,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>16167</t>
+          <t>17972</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>9335</t>
+          <t>11064</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>25826</t>
+          <t>26433</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,36%</t>
         </is>
       </c>
     </row>
@@ -4579,32 +4579,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>18495</t>
+          <t>24959</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>10465</t>
+          <t>15559</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>30683</t>
+          <t>37808</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4614,32 +4614,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>11131</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>4898</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>18524</t>
+          <t>25160</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4649,32 +4649,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>29626</t>
+          <t>41242</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>18406</t>
+          <t>29409</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>42241</t>
+          <t>56920</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -4692,67 +4692,67 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>12568</t>
+          <t>11977</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>4114</t>
+          <t>4439</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>27514</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>2,33%</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>3408</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>1220</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>7683</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
           <t>0,41%</t>
         </is>
       </c>
-      <c r="I39" s="2" t="inlineStr">
-        <is>
-          <t>2,71%</t>
-        </is>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>3387</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
-        <is>
-          <t>851</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>7867</t>
-        </is>
-      </c>
-      <c r="N39" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4762,32 +4762,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>15956</t>
+          <t>15385</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>7019</t>
+          <t>7903</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>34540</t>
+          <t>30618</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -4805,32 +4805,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>9815</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2825</t>
+          <t>2768</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>25578</t>
+          <t>23515</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>723</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
@@ -4850,12 +4850,12 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>4921</t>
+          <t>3686</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
@@ -4865,7 +4865,7 @@
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4875,32 +4875,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>10550</t>
+          <t>9954</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>3050</t>
+          <t>3569</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>32348</t>
+          <t>27671</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -4918,32 +4918,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>16634</t>
+          <t>17691</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>9674</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>26800</t>
+          <t>27945</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4953,32 +4953,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>7975</t>
+          <t>8318</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>3254</t>
+          <t>4304</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>15117</t>
+          <t>15013</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4988,32 +4988,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>24610</t>
+          <t>26008</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>16054</t>
+          <t>17426</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>37274</t>
+          <t>38969</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -5031,32 +5031,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>92406</t>
+          <t>111364</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>73936</t>
+          <t>92641</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>113985</t>
+          <t>135849</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5066,32 +5066,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>51084</t>
+          <t>60097</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>25109</t>
+          <t>47567</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>71788</t>
+          <t>74001</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5101,32 +5101,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>143490</t>
+          <t>171462</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>95661</t>
+          <t>148019</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>172639</t>
+          <t>199320</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>10,29%</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5144,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>5657</t>
+          <t>5207</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5179,7 +5179,7 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>695</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>3485</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0,06%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>1740</t>
+          <t>1982</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>6423</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5239,7 +5239,7 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>810</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3849</t>
+          <t>4604</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
@@ -5317,7 +5317,7 @@
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5327,7 +5327,7 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>741</t>
+          <t>810</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4079</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5352,7 +5352,7 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
     </row>
@@ -5370,7 +5370,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>6011</t>
+          <t>6708</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -5395,7 +5395,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5405,7 +5405,7 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>1649</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
@@ -5415,12 +5415,12 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>5734</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5440,32 +5440,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>2836</t>
+          <t>2935</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>677</t>
+          <t>802</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>7867</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -5483,32 +5483,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>52303</t>
+          <t>56794</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>37654</t>
+          <t>41861</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>69058</t>
+          <t>75152</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5518,32 +5518,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>15402</t>
+          <t>17121</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>11131</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>25226</t>
+          <t>26034</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5553,32 +5553,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>67705</t>
+          <t>73914</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>46262</t>
+          <t>58006</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>88197</t>
+          <t>92653</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,78%</t>
         </is>
       </c>
     </row>
@@ -5596,32 +5596,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>855514</t>
+          <t>926914</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>827290</t>
+          <t>898152</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>878919</t>
+          <t>952594</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>81,54%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5631,32 +5631,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>871705</t>
+          <t>735507</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>842334</t>
+          <t>718890</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>907245</t>
+          <t>751649</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>91,89%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>90,84%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5666,32 +5666,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>1727219</t>
+          <t>1662421</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1686500</t>
+          <t>1630226</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1799144</t>
+          <t>1694192</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>85,9%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>87,46%</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -5723,12 +5723,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>10069</t>
+          <t>7743</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5748,32 +5748,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>7300</t>
+          <t>7961</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>4006</t>
+          <t>4221</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>14628</t>
+          <t>15292</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5783,22 +5783,22 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>9790</t>
+          <t>10146</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>5471</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>16536</t>
+          <t>17626</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
@@ -5808,7 +5808,7 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -5826,32 +5826,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>8043</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>6452</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>16195</t>
+          <t>21416</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5861,32 +5861,32 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>23783</t>
+          <t>30492</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>15620</t>
+          <t>21110</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>39124</t>
+          <t>45302</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -5896,32 +5896,32 @@
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>31826</t>
+          <t>42412</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>22214</t>
+          <t>31882</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>44075</t>
+          <t>59915</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -5939,7 +5939,7 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>2117</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
@@ -5949,12 +5949,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>7484</t>
+          <t>7138</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5974,17 +5974,17 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>8061</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>4279</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>15767</t>
+          <t>16358</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -5994,12 +5994,12 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6009,32 +6009,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>10178</t>
+          <t>10742</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>5393</t>
+          <t>5912</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>18853</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>3205</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
@@ -6062,92 +6062,92 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>11539</t>
+          <t>10331</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>1,94%</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>5697</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>2712</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>10940</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="H51" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>2,54%</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>5640</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
-        <is>
-          <t>2451</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr">
-        <is>
-          <t>11078</t>
-        </is>
-      </c>
-      <c r="N51" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>1,37%</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R51" s="2" t="inlineStr">
+        <is>
+          <t>8467</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>4340</t>
+        </is>
+      </c>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>15705</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="P51" s="2" t="inlineStr">
-        <is>
-          <t>1,49%</t>
-        </is>
-      </c>
-      <c r="Q51" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R51" s="2" t="inlineStr">
-        <is>
-          <t>8845</t>
-        </is>
-      </c>
-      <c r="S51" s="2" t="inlineStr">
-        <is>
-          <t>4255</t>
-        </is>
-      </c>
-      <c r="T51" s="2" t="inlineStr">
-        <is>
-          <t>16330</t>
-        </is>
-      </c>
-      <c r="U51" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="V51" s="2" t="inlineStr">
-        <is>
-          <t>0,36%</t>
-        </is>
-      </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,18%</t>
         </is>
       </c>
     </row>
@@ -6165,32 +6165,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>9948</t>
+          <t>11038</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>4542</t>
+          <t>5571</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>18037</t>
+          <t>21137</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6200,32 +6200,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>13738</t>
+          <t>16605</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>8640</t>
+          <t>11075</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>20992</t>
+          <t>24401</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6235,32 +6235,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>23687</t>
+          <t>27642</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>16014</t>
+          <t>20408</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>33543</t>
+          <t>39127</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -6278,32 +6278,32 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>61355</t>
+          <t>72226</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>47547</t>
+          <t>56682</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>77471</t>
+          <t>90326</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
@@ -6313,32 +6313,32 @@
       </c>
       <c r="K53" s="2" t="inlineStr">
         <is>
-          <t>99665</t>
+          <t>118147</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>81412</t>
+          <t>102015</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>118235</t>
+          <t>138975</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>17,43%</t>
         </is>
       </c>
       <c r="Q53" s="2" t="inlineStr">
@@ -6348,32 +6348,32 @@
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>161019</t>
+          <t>190373</t>
         </is>
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>136608</t>
+          <t>165834</t>
         </is>
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>182174</t>
+          <t>218252</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>16,4%</t>
         </is>
       </c>
     </row>
@@ -6391,7 +6391,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>1897</t>
+          <t>1502</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
@@ -6401,92 +6401,92 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>8289</t>
+          <t>9189</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3376</t>
+        </is>
+      </c>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
           <t>0,42%</t>
         </is>
       </c>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="Q54" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R54" s="2" t="inlineStr">
+        <is>
+          <t>2210</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T54" s="2" t="inlineStr">
+        <is>
+          <t>9293</t>
+        </is>
+      </c>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>803</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>2057</t>
-        </is>
-      </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T54" s="2" t="inlineStr">
-        <is>
-          <t>9102</t>
-        </is>
-      </c>
-      <c r="U54" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -6652,32 +6652,32 @@
       </c>
       <c r="K56" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>736</t>
         </is>
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>4015</t>
+          <t>6331</t>
         </is>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q56" s="2" t="inlineStr">
@@ -6687,32 +6687,32 @@
       </c>
       <c r="R56" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>2349</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>737</t>
         </is>
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>4353</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>0,01%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,51%</t>
         </is>
       </c>
     </row>
@@ -6730,32 +6730,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>31841</t>
+          <t>41914</t>
         </is>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>21921</t>
+          <t>30886</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>44327</t>
+          <t>61462</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
@@ -6765,32 +6765,32 @@
       </c>
       <c r="K57" s="2" t="inlineStr">
         <is>
-          <t>39359</t>
+          <t>46148</t>
         </is>
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>29832</t>
+          <t>35271</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>51937</t>
+          <t>58040</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q57" s="2" t="inlineStr">
@@ -6800,32 +6800,32 @@
       </c>
       <c r="R57" s="2" t="inlineStr">
         <is>
-          <t>71199</t>
+          <t>88062</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>56555</t>
+          <t>71492</t>
         </is>
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>87699</t>
+          <t>109728</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -6843,32 +6843,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>368835</t>
+          <t>428084</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>349508</t>
+          <t>405651</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>384927</t>
+          <t>445777</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
@@ -6878,32 +6878,32 @@
       </c>
       <c r="K58" s="2" t="inlineStr">
         <is>
-          <t>605303</t>
+          <t>636222</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>583877</t>
+          <t>614915</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>628324</t>
+          <t>655512</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="Q58" s="2" t="inlineStr">
@@ -6913,39 +6913,39 @@
       </c>
       <c r="R58" s="2" t="inlineStr">
         <is>
-          <t>974139</t>
+          <t>1064307</t>
         </is>
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>949274</t>
+          <t>1033878</t>
         </is>
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>1003661</t>
+          <t>1090848</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>79,99%</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>79,35%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>81,99%</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>1790</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>10278</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -6985,7 +6985,7 @@
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="K59" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="L59" s="2" t="inlineStr">
@@ -7005,7 +7005,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>3979</t>
+          <t>5760</t>
         </is>
       </c>
       <c r="N59" s="2" t="inlineStr">
@@ -7020,7 +7020,7 @@
       </c>
       <c r="P59" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q59" s="2" t="inlineStr">
@@ -7030,32 +7030,32 @@
       </c>
       <c r="R59" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>3163</t>
         </is>
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>620</t>
         </is>
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>4837</t>
+          <t>11779</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>0,06%</t>
         </is>
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
@@ -7073,7 +7073,7 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>1822</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>8004</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
@@ -7098,7 +7098,7 @@
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
@@ -7108,32 +7108,32 @@
       </c>
       <c r="K60" s="2" t="inlineStr">
         <is>
-          <t>20853</t>
+          <t>24232</t>
         </is>
       </c>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>15391</t>
         </is>
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>38489</t>
+          <t>40314</t>
         </is>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="Q60" s="2" t="inlineStr">
@@ -7143,32 +7143,32 @@
       </c>
       <c r="R60" s="2" t="inlineStr">
         <is>
-          <t>21015</t>
+          <t>26054</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>11486</t>
+          <t>16788</t>
         </is>
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>38971</t>
+          <t>41882</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -7221,32 +7221,32 @@
       </c>
       <c r="K61" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>731</t>
+          <t>728</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>6488</t>
+          <t>7111</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q61" s="2" t="inlineStr">
@@ -7256,32 +7256,32 @@
       </c>
       <c r="R61" s="2" t="inlineStr">
         <is>
-          <t>2788</t>
+          <t>2857</t>
         </is>
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>724</t>
+          <t>714</t>
         </is>
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>7116</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,07%</t>
         </is>
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,69%</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="K62" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>692</t>
         </is>
       </c>
       <c r="L62" s="2" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>3751</t>
+          <t>4144</t>
         </is>
       </c>
       <c r="N62" s="2" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="R62" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>692</t>
         </is>
       </c>
       <c r="S62" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="T62" s="2" t="inlineStr">
         <is>
-          <t>3261</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="U62" s="2" t="inlineStr">
@@ -7394,7 +7394,7 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>2070</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>11343</t>
+          <t>13177</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -7437,7 +7437,7 @@
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
@@ -7447,67 +7447,67 @@
       </c>
       <c r="K63" s="2" t="inlineStr">
         <is>
-          <t>9921</t>
+          <t>10728</t>
         </is>
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>5348</t>
+          <t>5535</t>
         </is>
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>17725</t>
+          <t>19526</t>
         </is>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
         <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R63" s="2" t="inlineStr">
+        <is>
+          <t>13169</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>7680</t>
+        </is>
+      </c>
+      <c r="T63" s="2" t="inlineStr">
+        <is>
+          <t>24964</t>
+        </is>
+      </c>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>0,76%</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
           <t>2,47%</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R63" s="2" t="inlineStr">
-        <is>
-          <t>11991</t>
-        </is>
-      </c>
-      <c r="S63" s="2" t="inlineStr">
-        <is>
-          <t>6016</t>
-        </is>
-      </c>
-      <c r="T63" s="2" t="inlineStr">
-        <is>
-          <t>21636</t>
-        </is>
-      </c>
-      <c r="U63" s="2" t="inlineStr">
-        <is>
-          <t>1,29%</t>
-        </is>
-      </c>
-      <c r="V63" s="2" t="inlineStr">
-        <is>
-          <t>0,65%</t>
-        </is>
-      </c>
-      <c r="W63" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -7525,32 +7525,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>11559</t>
+          <t>14503</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>4243</t>
+          <t>5943</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>28192</t>
+          <t>27352</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
@@ -7560,32 +7560,32 @@
       </c>
       <c r="K64" s="2" t="inlineStr">
         <is>
-          <t>95448</t>
+          <t>104707</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>79666</t>
+          <t>88767</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>115709</t>
+          <t>123824</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,14%</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q64" s="2" t="inlineStr">
@@ -7595,32 +7595,32 @@
       </c>
       <c r="R64" s="2" t="inlineStr">
         <is>
-          <t>107007</t>
+          <t>119210</t>
         </is>
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>87293</t>
+          <t>98617</t>
         </is>
       </c>
       <c r="T64" s="2" t="inlineStr">
         <is>
-          <t>132492</t>
+          <t>142086</t>
         </is>
       </c>
       <c r="U64" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -7673,32 +7673,32 @@
       </c>
       <c r="K65" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>638</t>
+          <t>669</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>6270</t>
+          <t>6424</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q65" s="2" t="inlineStr">
@@ -7708,17 +7708,17 @@
       </c>
       <c r="R65" s="2" t="inlineStr">
         <is>
-          <t>2177</t>
+          <t>2331</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>664</t>
         </is>
       </c>
       <c r="T65" s="2" t="inlineStr">
         <is>
-          <t>6426</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="U65" s="2" t="inlineStr">
@@ -7733,7 +7733,7 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -7786,7 +7786,7 @@
       </c>
       <c r="K66" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>11176</t>
+          <t>10284</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="O66" s="2" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="P66" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q66" s="2" t="inlineStr">
@@ -7821,7 +7821,7 @@
       </c>
       <c r="R66" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>2017</t>
         </is>
       </c>
       <c r="S66" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="T66" s="2" t="inlineStr">
         <is>
-          <t>8842</t>
+          <t>13371</t>
         </is>
       </c>
       <c r="U66" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="V66" s="2" t="inlineStr">
@@ -7846,7 +7846,7 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,32%</t>
         </is>
       </c>
     </row>
@@ -7899,7 +7899,7 @@
       </c>
       <c r="K67" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>740</t>
         </is>
       </c>
       <c r="L67" s="2" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>4176</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="N67" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="P67" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="Q67" s="2" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="R67" s="2" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>740</t>
         </is>
       </c>
       <c r="S67" s="2" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="T67" s="2" t="inlineStr">
         <is>
-          <t>4107</t>
+          <t>3665</t>
         </is>
       </c>
       <c r="U67" s="2" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -7977,32 +7977,32 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>6866</t>
+          <t>6656</t>
         </is>
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>1383</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>22561</t>
+          <t>19803</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
@@ -8012,32 +8012,32 @@
       </c>
       <c r="K68" s="2" t="inlineStr">
         <is>
-          <t>50586</t>
+          <t>55667</t>
         </is>
       </c>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>39608</t>
+          <t>43199</t>
         </is>
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>70456</t>
+          <t>71531</t>
         </is>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="Q68" s="2" t="inlineStr">
@@ -8047,32 +8047,32 @@
       </c>
       <c r="R68" s="2" t="inlineStr">
         <is>
-          <t>57451</t>
+          <t>62322</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>43673</t>
+          <t>48005</t>
         </is>
       </c>
       <c r="T68" s="2" t="inlineStr">
         <is>
-          <t>78550</t>
+          <t>79916</t>
         </is>
       </c>
       <c r="U68" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>7,91%</t>
         </is>
       </c>
     </row>
@@ -8090,32 +8090,32 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>198376</t>
+          <t>192866</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>179612</t>
+          <t>176877</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>206971</t>
+          <t>202834</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
@@ -8125,32 +8125,32 @@
       </c>
       <c r="K69" s="2" t="inlineStr">
         <is>
-          <t>588073</t>
+          <t>648918</t>
         </is>
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>565959</t>
+          <t>626433</t>
         </is>
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>606669</t>
+          <t>670009</t>
         </is>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>78,83%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,06%</t>
         </is>
       </c>
       <c r="Q69" s="2" t="inlineStr">
@@ -8160,32 +8160,32 @@
       </c>
       <c r="R69" s="2" t="inlineStr">
         <is>
-          <t>786448</t>
+          <t>841783</t>
         </is>
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>761479</t>
+          <t>815047</t>
         </is>
       </c>
       <c r="T69" s="2" t="inlineStr">
         <is>
-          <t>810554</t>
+          <t>867366</t>
         </is>
       </c>
       <c r="U69" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>83,37%</t>
         </is>
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>81,69%</t>
+          <t>80,72%</t>
         </is>
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>85,9%</t>
         </is>
       </c>
     </row>
@@ -8207,32 +8207,32 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>30787</t>
+          <t>34742</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>20149</t>
+          <t>24547</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>44553</t>
+          <t>49558</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -8242,27 +8242,27 @@
       </c>
       <c r="K70" s="2" t="inlineStr">
         <is>
-          <t>22913</t>
+          <t>25499</t>
         </is>
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>16115</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>34033</t>
+          <t>34956</t>
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8277,32 +8277,32 @@
       </c>
       <c r="R70" s="2" t="inlineStr">
         <is>
-          <t>53701</t>
+          <t>60241</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>39356</t>
+          <t>45634</t>
         </is>
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>68612</t>
+          <t>76108</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V70" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,11%</t>
         </is>
       </c>
     </row>
@@ -8320,32 +8320,32 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>45889</t>
+          <t>63729</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>32891</t>
+          <t>47258</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>62729</t>
+          <t>81674</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
@@ -8355,32 +8355,32 @@
       </c>
       <c r="K71" s="2" t="inlineStr">
         <is>
-          <t>63123</t>
+          <t>80958</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>46272</t>
+          <t>64228</t>
         </is>
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>83400</t>
+          <t>100246</t>
         </is>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q71" s="2" t="inlineStr">
@@ -8390,32 +8390,32 @@
       </c>
       <c r="R71" s="2" t="inlineStr">
         <is>
-          <t>109012</t>
+          <t>144688</t>
         </is>
       </c>
       <c r="S71" s="2" t="inlineStr">
         <is>
-          <t>86343</t>
+          <t>121722</t>
         </is>
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>136352</t>
+          <t>173672</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -8433,32 +8433,32 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>20617</t>
+          <t>21822</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>10534</t>
+          <t>12991</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>37985</t>
+          <t>37880</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
@@ -8468,22 +8468,22 @@
       </c>
       <c r="K72" s="2" t="inlineStr">
         <is>
-          <t>16257</t>
+          <t>17734</t>
         </is>
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>10831</t>
         </is>
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>24993</t>
+          <t>26534</t>
         </is>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
@@ -8493,7 +8493,7 @@
       </c>
       <c r="P72" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="Q72" s="2" t="inlineStr">
@@ -8503,32 +8503,32 @@
       </c>
       <c r="R72" s="2" t="inlineStr">
         <is>
-          <t>36875</t>
+          <t>39556</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>25166</t>
+          <t>27109</t>
         </is>
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>54039</t>
+          <t>57038</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -8546,17 +8546,17 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>18421</t>
+          <t>18745</t>
         </is>
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>8824</t>
+          <t>9833</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>37503</t>
+          <t>34645</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
@@ -8566,12 +8566,12 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
@@ -8581,17 +8581,17 @@
       </c>
       <c r="K73" s="2" t="inlineStr">
         <is>
-          <t>12032</t>
+          <t>12153</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>7038</t>
+          <t>6918</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>20800</t>
+          <t>20176</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -8601,12 +8601,12 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="Q73" s="2" t="inlineStr">
@@ -8616,32 +8616,32 @@
       </c>
       <c r="R73" s="2" t="inlineStr">
         <is>
-          <t>30453</t>
+          <t>30898</t>
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
         <is>
-          <t>18924</t>
+          <t>20024</t>
         </is>
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>47906</t>
+          <t>47686</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V73" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -8659,32 +8659,32 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>41808</t>
+          <t>44895</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>29128</t>
+          <t>32820</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>57159</t>
+          <t>61086</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
@@ -8694,32 +8694,32 @@
       </c>
       <c r="K74" s="2" t="inlineStr">
         <is>
-          <t>39121</t>
+          <t>43718</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>28697</t>
+          <t>34013</t>
         </is>
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>51066</t>
+          <t>57614</t>
         </is>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q74" s="2" t="inlineStr">
@@ -8729,32 +8729,32 @@
       </c>
       <c r="R74" s="2" t="inlineStr">
         <is>
-          <t>80929</t>
+          <t>88613</t>
         </is>
       </c>
       <c r="S74" s="2" t="inlineStr">
         <is>
-          <t>63316</t>
+          <t>72581</t>
         </is>
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>98965</t>
+          <t>108747</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="V74" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,59%</t>
         </is>
       </c>
     </row>
@@ -8772,32 +8772,32 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>245553</t>
+          <t>288027</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>189342</t>
+          <t>256062</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>281407</t>
+          <t>324119</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
@@ -8807,32 +8807,32 @@
       </c>
       <c r="K75" s="2" t="inlineStr">
         <is>
-          <t>299893</t>
+          <t>344139</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>239750</t>
+          <t>311457</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>334891</t>
+          <t>376785</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q75" s="2" t="inlineStr">
@@ -8842,32 +8842,32 @@
       </c>
       <c r="R75" s="2" t="inlineStr">
         <is>
-          <t>545446</t>
+          <t>632166</t>
         </is>
       </c>
       <c r="S75" s="2" t="inlineStr">
         <is>
-          <t>472955</t>
+          <t>586807</t>
         </is>
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>606074</t>
+          <t>682161</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="V75" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,97%</t>
         </is>
       </c>
     </row>
@@ -8885,32 +8885,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>11312</t>
+          <t>12094</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>5985</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>20828</t>
+          <t>22801</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
@@ -8920,27 +8920,27 @@
       </c>
       <c r="K76" s="2" t="inlineStr">
         <is>
-          <t>6834</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>3673</t>
+          <t>4320</t>
         </is>
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>13008</t>
+          <t>13349</t>
         </is>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,12%</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -8955,32 +8955,32 @@
       </c>
       <c r="R76" s="2" t="inlineStr">
         <is>
-          <t>18146</t>
+          <t>20132</t>
         </is>
       </c>
       <c r="S76" s="2" t="inlineStr">
         <is>
-          <t>11068</t>
+          <t>12134</t>
         </is>
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>28757</t>
+          <t>29870</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="V76" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
     </row>
@@ -9033,22 +9033,22 @@
       </c>
       <c r="K77" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>546</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>8858</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="O77" s="2" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="P77" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="Q77" s="2" t="inlineStr">
@@ -9068,22 +9068,22 @@
       </c>
       <c r="R77" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="S77" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>615</t>
         </is>
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>12113</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="V77" s="2" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,18%</t>
         </is>
       </c>
     </row>
@@ -9111,7 +9111,7 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>1187</t>
+          <t>1130</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
@@ -9121,92 +9121,92 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>6390</t>
+          <t>5675</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
+          <t>0,03%</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>0,17%</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>4893</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>10194</t>
+        </is>
+      </c>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>0,14%</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>0,06%</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R78" s="2" t="inlineStr">
+        <is>
+          <t>6023</t>
+        </is>
+      </c>
+      <c r="S78" s="2" t="inlineStr">
+        <is>
+          <t>2531</t>
+        </is>
+      </c>
+      <c r="T78" s="2" t="inlineStr">
+        <is>
+          <t>12132</t>
+        </is>
+      </c>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>0,09%</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
           <t>0,04%</t>
         </is>
       </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>3362</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
-        <is>
-          <t>1068</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>8129</t>
-        </is>
-      </c>
-      <c r="N78" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="O78" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="P78" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="Q78" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="R78" s="2" t="inlineStr">
-        <is>
-          <t>4549</t>
-        </is>
-      </c>
-      <c r="S78" s="2" t="inlineStr">
-        <is>
-          <t>1602</t>
-        </is>
-      </c>
-      <c r="T78" s="2" t="inlineStr">
-        <is>
-          <t>9691</t>
-        </is>
-      </c>
-      <c r="U78" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="V78" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,18%</t>
         </is>
       </c>
     </row>
@@ -9224,32 +9224,32 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>134173</t>
+          <t>154907</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>102764</t>
+          <t>128935</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>161832</t>
+          <t>185956</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
@@ -9259,32 +9259,32 @@
       </c>
       <c r="K79" s="2" t="inlineStr">
         <is>
-          <t>125076</t>
+          <t>144058</t>
         </is>
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>100318</t>
+          <t>124529</t>
         </is>
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>148552</t>
+          <t>166647</t>
         </is>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="Q79" s="2" t="inlineStr">
@@ -9294,32 +9294,32 @@
       </c>
       <c r="R79" s="2" t="inlineStr">
         <is>
-          <t>259249</t>
+          <t>298964</t>
         </is>
       </c>
       <c r="S79" s="2" t="inlineStr">
         <is>
-          <t>213628</t>
+          <t>264803</t>
         </is>
       </c>
       <c r="T79" s="2" t="inlineStr">
         <is>
-          <t>294934</t>
+          <t>335187</t>
         </is>
       </c>
       <c r="U79" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="V79" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -9337,32 +9337,32 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>2881941</t>
+          <t>2863014</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>2828415</t>
+          <t>2819736</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>2972609</t>
+          <t>2908382</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>85,79%</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
@@ -9372,32 +9372,32 @@
       </c>
       <c r="K80" s="2" t="inlineStr">
         <is>
-          <t>2957728</t>
+          <t>2998662</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>2913566</t>
+          <t>2959935</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3047605</t>
+          <t>3035322</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>84,44%</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="Q80" s="2" t="inlineStr">
@@ -9407,32 +9407,32 @@
       </c>
       <c r="R80" s="2" t="inlineStr">
         <is>
-          <t>5839669</t>
+          <t>5861676</t>
         </is>
       </c>
       <c r="S80" s="2" t="inlineStr">
         <is>
-          <t>5760958</t>
+          <t>5803718</t>
         </is>
       </c>
       <c r="T80" s="2" t="inlineStr">
         <is>
-          <t>5952717</t>
+          <t>5916091</t>
         </is>
       </c>
       <c r="U80" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="V80" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>86,46%</t>
         </is>
       </c>
     </row>
